--- a/data/balance_sheet.xlsx
+++ b/data/balance_sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57a7ad308045bdf4/Desktop/AI Workings/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57a7ad308045bdf4/Desktop/trr-workflow/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{036B691F-B34D-48E3-855F-67181110D3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D257997E-1591-4ACC-9019-647F287D02EF}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{036B691F-B34D-48E3-855F-67181110D3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B460CF4E-05FA-4939-8E15-3EFFA5FF289A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26E42CC9-878F-4166-B8BB-7A279576AA66}"/>
   </bookViews>
@@ -350,10 +350,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -930,7 +926,7 @@
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="16">
-        <v>70.400000000000006</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
